--- a/Shared/XLS/Pet.xlsx
+++ b/Shared/XLS/Pet.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>!Table</t>
   </si>
@@ -44,14 +44,14 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
   </si>
   <si>
     <t>고양이1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고양이2</t>
@@ -83,7 +83,7 @@
       </rPr>
       <t>odel</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -100,7 +100,7 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Prefab_Pet_01</t>
@@ -122,15 +122,15 @@
   </si>
   <si>
     <t>PetEnhance</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Grade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
@@ -151,38 +151,6 @@
     <t>Pet_01</t>
   </si>
   <si>
-    <t>Pet_01</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Enum</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Table</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>Pet_02</t>
   </si>
   <si>
@@ -208,11 +176,11 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaxLevel</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Option</t>
@@ -222,15 +190,15 @@
   </si>
   <si>
     <t>Opt_ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Opt_Val</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Opt_Step</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>OPT_MAX_HP_ADD</t>
@@ -249,71 +217,79 @@
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Ruby</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostCurrencyID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostCurrencyValue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CostCurrencyMult</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>FromGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ToGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>PetPromotion</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EquipText</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>근처의 아이템을 자동으로 획득한다.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Image</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Pet</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!Pet</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Table</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -434,51 +410,51 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -762,7 +738,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -774,7 +750,7 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.375" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.625" style="1" customWidth="1"/>
@@ -788,10 +764,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -806,28 +782,28 @@
         <v>11</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="6" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -836,28 +812,28 @@
         <v>12</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="B4" s="1" t="s">
-        <v>28</v>
+      <c r="B4" s="1">
+        <v>1040200001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -872,7 +848,7 @@
         <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H4" s="1">
         <v>10</v>
@@ -881,12 +857,12 @@
         <v>0.1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="1" t="s">
-        <v>30</v>
+      <c r="B5" s="1">
+        <v>1040200002</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>6</v>
@@ -895,13 +871,13 @@
         <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5" s="1">
         <v>50</v>
@@ -910,13 +886,13 @@
         <v>0.1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="1" t="s">
-        <v>31</v>
+      <c r="B6" s="1">
+        <v>1040200003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>7</v>
@@ -925,13 +901,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H6" s="1">
         <v>10</v>
@@ -940,13 +916,13 @@
         <v>0.05</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="1" t="s">
-        <v>32</v>
+      <c r="B7" s="1">
+        <v>1040200004</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -955,13 +931,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H7" s="1">
         <v>0.1</v>
@@ -970,12 +946,12 @@
         <v>1E-4</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="1" t="s">
-        <v>33</v>
+      <c r="B8" s="1">
+        <v>1040200005</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>9</v>
@@ -984,13 +960,13 @@
         <v>17</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H8" s="1">
         <v>0.1</v>
@@ -999,12 +975,12 @@
         <v>1E-4</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="1" t="s">
-        <v>34</v>
+      <c r="B9" s="1">
+        <v>1040200006</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
@@ -1013,13 +989,13 @@
         <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1">
         <v>0.01</v>
@@ -1028,7 +1004,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1143,7 +1119,7 @@
       <c r="A40" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1184,16 +1160,16 @@
         <v>21</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="H2" s="6"/>
       <c r="J2" s="6"/>
@@ -1207,16 +1183,16 @@
         <v>20</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="J3" s="6"/>
     </row>
@@ -1232,7 +1208,7 @@
         <v>20</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F4" s="9">
         <v>100</v>
@@ -1254,7 +1230,7 @@
         <v>40</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F5" s="9">
         <v>5000</v>
@@ -1277,7 +1253,7 @@
         <v>60</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" s="9">
         <v>20000</v>
@@ -1300,7 +1276,7 @@
         <v>80</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F7" s="9">
         <v>80000</v>
@@ -1322,7 +1298,7 @@
         <v>100</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F8" s="9">
         <v>300000</v>
@@ -1481,7 +1457,7 @@
       <c r="G39" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1504,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1513,16 +1489,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1537,10 +1513,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1555,7 +1531,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" s="9">
         <v>100</v>
@@ -1572,7 +1548,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F5" s="9">
         <v>200</v>
@@ -1590,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F6" s="9">
         <v>300</v>
@@ -1608,7 +1584,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F7" s="9">
         <v>600</v>
@@ -1666,7 +1642,7 @@
       <c r="E39" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>